--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_FitGap_BRD-03_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_FitGap_BRD-03_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Functional requirements of the FRS v1.2</t>
+          <t>Functional requirements of the FRS v1.3</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr"/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_FitGap_BRD-03_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_FitGap_BRD-03_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>What the platform offers out of the box</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>What the platform offers out of the box</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_FitGap_BRD-03_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_FitGap_BRD-03_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$C$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fit-Gap'!$A$4:$I$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Fit-Gap'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -680,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -690,13 +690,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -725,6 +728,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -797,6 +801,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -857,13 +862,14 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>One row per BRD requirement: BRD text, out of the box, BIBS, best practice, fit</t>
+          <t>One row per BRD requirement: BRD text, out of the box, best practice, fit</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
         <v>31</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="9" t="inlineStr">
         <is>
@@ -879,7 +885,7 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>BIBS meets the requirement as specified</t>
+          <t>The system meets the requirement as specified</t>
         </is>
       </c>
     </row>
@@ -919,6 +925,8 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="19" t="inlineStr">
         <is>
@@ -953,7 +961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -976,6 +984,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1132,12 +1141,12 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>What BIBS offers for BDOI</t>
+          <t>Insurance-broking best practice</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Capability and configuration of BIBS for this BRD</t>
+          <t>Philippine market and international broking practice</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr"/>
@@ -1150,15 +1159,19 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>Insurance-broking best practice</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Philippine market and international broking practice</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr"/>
+          <t>Fit class</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Fit, Configure, Extend, Recommend change</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -1168,19 +1181,15 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Recommendation</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Fit class</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Fit, Configure, Extend, Recommend change</t>
-        </is>
-      </c>
+          <t>What the project team recommends</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -1190,12 +1199,12 @@
       </c>
       <c r="B15" s="21" t="inlineStr">
         <is>
-          <t>Recommendation</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>What the project team recommends</t>
+          <t>Effect on the business</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
@@ -1208,36 +1217,18 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Feature List rows</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Effect on the business</t>
+          <t>Rows of the programme Feature List workbook</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Fit-Gap</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>Feature List rows</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Rows of the programme Feature List workbook</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D17"/>
+  <autoFilter ref="A4:D16"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1407,7 +1398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1415,11 +1406,10 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1432,7 +1422,7 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>One row per BRD requirement: BRD text, out of the box, BIBS, best practice, fit</t>
+          <t>One row per BRD requirement: BRD text, out of the box, best practice, fit</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1436,6 @@
       <c r="G3" s="24" t="n"/>
       <c r="H3" s="24" t="n"/>
       <c r="I3" s="24" t="n"/>
-      <c r="J3" s="24" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
@@ -1471,30 +1460,25 @@
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
-          <t>What BIBS offers for BDOI</t>
+          <t>Insurance-broking best practice</t>
         </is>
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>Insurance-broking best practice</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Recommendation</t>
         </is>
       </c>
       <c r="H4" s="25" t="inlineStr">
         <is>
-          <t>Recommendation</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="I4" s="25" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="J4" s="25" t="inlineStr">
         <is>
           <t>Feature List rows</t>
         </is>
@@ -1524,31 +1508,26 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>One product hierarchy: line, cover type / sub-line, subtype, product (risk code), coverages and perils per line, under maker-checker.</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
           <t>PRD-001: One product master shared by quoting, placement, accounting and reporting.
 PRD-002: A consistent product taxonomy (in line with ACORD line-of-business coding) across all lines.</t>
         </is>
       </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Configure</t>
+          <t>Load BDOI's sub-lines (Annex A) and the coverages per line; state the risk-code naming convention.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Load BDOI's sub-lines (Annex A) and the coverages per line; state the risk-code naming convention.</t>
+          <t>Product data consistent across New Business, Renewal and reports.</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>Product data consistent across New Business, Renewal and reports.</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>PRD-001, PRD-002</t>
         </is>
@@ -1580,33 +1559,28 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Clause library; insurer-specific coverages, deductibles, warranties and clauses on each package version; co-insurance roles and shares.</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
           <t>PRD-014: Standard wordings are held once and reused, so slips and schedules are consistent.
 PRD-015: Insurer-specific terms are structured data, not free text, so comparisons and slips are accurate.
 PRD-016: Only accredited insurers with authority are offered for each product.
 QPL-016: Co-insurance is common in the Philippine market and must flow to billing, remittance and claims.</t>
         </is>
       </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Configure</t>
+          <t>Load the clause library and the insurer terms of the packages in force (templates PM-03, PM-06).</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Load the clause library and the insurer terms of the packages in force (templates PM-03, PM-06).</t>
+          <t>Insurer variability kept as data, without IT.</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>Insurer variability kept as data, without IT.</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>PRD-014, PRD-015, PRD-016, QPL-016</t>
         </is>
@@ -1635,30 +1609,25 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Master Comparative Table per round with superseded masters kept; client views with chosen insurers and fields; PDF and Excel.</t>
+          <t>PRD-020: Comparisons are produced from captured terms, not re-keyed into spreadsheets.</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>PRD-020: Comparisons are produced from captured terms, not re-keyed into spreadsheets.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Adopt; BDOI to give the client layout.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Adopt; BDOI to give the client layout.</t>
+          <t>Auditable record of what the client saw.</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>Auditable record of what the client saw.</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>PRD-020</t>
         </is>
@@ -1687,30 +1656,25 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Negotiation rounds with revised slips; response outcomes including declines and counter-proposals; not proceeded with reason.</t>
+          <t>PRD-019: Programme negotiations are recorded in the system with each insurer's position per round.</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>PRD-019: Programme negotiations are recorded in the system with each insurer's position per round.</t>
+          <t>Configure</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Configure</t>
+          <t>Confirm the response list (BDOI: Approved, Not Covered, Others) and the maximum rounds.</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Confirm the response list (BDOI: Approved, Not Covered, Others) and the maximum rounds.</t>
+          <t>Negotiation outcomes reported consistently.</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>Negotiation outcomes reported consistently.</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>PRD-019</t>
         </is>
@@ -1739,30 +1703,25 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Role-based access with permissions per action; four-eyes rules; role changes through the User Access Maintenance process.</t>
+          <t>Access by role with segregation of duties; reviewed periodically.</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Access by role with segregation of duties; reviewed periodically.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Follow the User Access Maintenance FRS; confirm the role-to-action matrix of Annex J.5.</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Follow the User Access Maintenance FRS; confirm the role-to-action matrix of Annex J.5.</t>
+          <t>Access controlled; audit risk reduced.</t>
         </is>
       </c>
       <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>Access controlled; audit risk reduced.</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1791,30 +1750,25 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Post-setup validation of each package version by a user other than the maker, with checklist and test premium.</t>
+          <t>PRD-012: Four-eyes control on product and rate set-up before release, with the validation evidenced.</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>PRD-012: Four-eyes control on product and rate set-up before release, with the validation evidenced.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Name the validator role and the checklist items.</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Name the validator role and the checklist items.</t>
+          <t>No unvalidated package reaches sales.</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>No unvalidated package reaches sales.</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>PRD-012</t>
         </is>
@@ -1843,30 +1797,25 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Incentive rules on maintained products, under maker-checker; applied at booking; review notice when a product ends.</t>
+          <t>PRD-026: Incentive eligibility rules are maintained as controlled master data linked to products.</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>PRD-026: Incentive eligibility rules are maintained as controlled master data linked to products.</t>
+          <t>Configure</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Configure</t>
+          <t>Define the incentive types and load the rules (template PM-10).</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Define the incentive types and load the rules (template PM-10).</t>
+          <t>Incentives applied only to eligible products.</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Incentives applied only to eligible products.</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>PRD-026</t>
         </is>
@@ -1895,30 +1844,25 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Maintenance screen of incentive rules with history and successors.</t>
+          <t>PRD-026: Incentive eligibility rules are maintained as controlled master data linked to products.</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>PRD-026: Incentive eligibility rules are maintained as controlled master data linked to products.</t>
+          <t>Configure</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Configure</t>
+          <t>Define CPC2 and the other types.</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Define CPC2 and the other types.</t>
+          <t>CPC2 cannot be set up until defined.</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>CPC2 cannot be set up until defined.</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>PRD-026</t>
         </is>
@@ -1947,30 +1891,25 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Sign-in through BDO sign-in (Entra ID) once switched on; lock-out and sign-out per the User Access Maintenance FRS.</t>
+          <t>Single sign-on with the bank's directory and a second factor for privileged users.</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Single sign-on with the bank's directory and a second factor for privileged users.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Follow the User Access Maintenance FRS.</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Follow the User Access Maintenance FRS.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1999,30 +1938,25 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Menus, screens and actions by role; direct requests without the right are refused and logged.</t>
+          <t>Least privilege; access requests approved and logged.</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Least privilege; access requests approved and logged.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Follow the User Access Maintenance FRS.</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Follow the User Access Maintenance FRS.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2051,30 +1985,25 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Mandatory and product-specific fields per line; field rules (presence, list, range, pattern).</t>
+          <t>PRD-003: Risk data captured to a standard per line so insurers receive complete submissions.</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>PRD-003: Risk data captured to a standard per line so insurers receive complete submissions.</t>
+          <t>Configure</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Configure</t>
+          <t>Give the mandatory fields and rules per line (Annex A to C, template PM-02).</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Give the mandatory fields and rules per line (Annex A to C, template PM-02).</t>
+          <t>Complete risk data for insurers.</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>Complete risk data for insurers.</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>PRD-003</t>
         </is>
@@ -2103,30 +2032,25 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Validation rules by product, maintained by MBS under maker-checker.</t>
+          <t>PRD-004: Business users maintain validation rules without code changes.</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>PRD-004: Business users maintain validation rules without code changes.</t>
+          <t>Configure</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Configure</t>
+          <t>Give the rules per product type.</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Give the rules per product type.</t>
+          <t>Fewer returned requests.</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>Fewer returned requests.</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>PRD-004</t>
         </is>
@@ -2155,30 +2079,25 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Shared document templates with product-specific sections; versioned; layouts replaced without a release.</t>
+          <t>PRD-027: Business users maintain document layouts without code changes.</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>PRD-027: Business users maintain document layouts without code changes.</t>
+          <t>Configure</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Configure</t>
+          <t>Provide the layouts of the package documents (Annex Q); load Annex D and F as the slip templates.</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Provide the layouts of the package documents (Annex Q); load Annex D and F as the slip templates.</t>
+          <t>Documents in BDOI's layouts.</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>Documents in BDOI's layouts.</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>PRD-027</t>
         </is>
@@ -2207,30 +2126,25 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Expired and deactivated packages archived with their versions and documents; visible to authorized users; return to sale through a new request.</t>
+          <t>PRD-013: Retired products remain retrievable for servicing, claims and audit.</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>PRD-013: Retired products remain retrievable for servicing, claims and audit.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Confirm reactivation through a package request (C11).</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>Confirm reactivation through a package request (C11).</t>
+          <t>History kept for servicing and audit.</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>History kept for servicing and audit.</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>PRD-013</t>
         </is>
@@ -2260,31 +2174,26 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>New business priced on the version in force; other rates only with an approved rate exception; version kept on quotation, account and invoice.</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
           <t>PRD-010: Product and rate changes are versioned, never overwritten.
 PRD-011: Old rates cannot be used for new business without an approved exception, and each transaction shows which rate version priced it.</t>
         </is>
       </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Confirm the approver and validity of rate exceptions.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Confirm the approver and validity of rate exceptions.</t>
+          <t>Outdated rates cannot be used.</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>Outdated rates cannot be used.</t>
-        </is>
-      </c>
-      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>PRD-010, PRD-011</t>
         </is>
@@ -2314,31 +2223,26 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Package Request Form with numbering, documents, Marketing approval and routing by source.</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
           <t>PRD-018: New products follow a documented approval path before negotiation starts.
 ADM-013: Configurable, gap-controlled numbering per document.</t>
         </is>
       </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Extend</t>
+          <t>Adopt BDOI's TL, TH, UH sequence and the Annex E fields (platform change).</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's TL, TH, UH sequence and the Annex E fields (platform change).</t>
+          <t>Requests reach TSU complete and approved.</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>Requests reach TSU complete and approved.</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>PRD-018, ADM-013</t>
         </is>
@@ -2367,30 +2271,25 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>TSU Team Lead recommendation and TSU Head approval, never by the recommender.</t>
+          <t>PRD-018: New products follow a documented approval path before negotiation starts.</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>PRD-018: New products follow a documented approval path before negotiation starts.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Keep the two TSU steps of BRPM.009 (C06).</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Keep the two TSU steps of BRPM.009 (C06).</t>
+          <t>Accountable TSU review.</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>Accountable TSU review.</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>PRD-018</t>
         </is>
@@ -2419,30 +2318,25 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Negotiation by TSU with insurers in rounds; terms final; review of negotiated terms.</t>
+          <t>PRD-019: Programme negotiations are recorded in the system with each insurer's position per round.</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>PRD-019: Programme negotiations are recorded in the system with each insurer's position per round.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Adopt.</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Adopt.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>PRD-019</t>
         </is>
@@ -2471,30 +2365,25 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Requests to create, amend, update, renew, reactivate or deactivate a package, visible in the request list.</t>
+          <t>PRD-018: New products follow a documented approval path before negotiation starts.</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>PRD-018: New products follow a documented approval path before negotiation starts.</t>
+          <t>Recommend change</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Recommend change</t>
+          <t>Deactivation in place of deletion (records kept).</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Deactivation in place of deletion (records kept).</t>
+          <t>No loss of history.</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>No loss of history.</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>PRD-018</t>
         </is>
@@ -2523,30 +2412,25 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Quotation Slip approved and sent from the system to each insurer as a protected document; send log and resend.</t>
+          <t>PRD-019: Programme negotiations are recorded in the system with each insurer's position per round.</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>PRD-019: Programme negotiations are recorded in the system with each insurer's position per round.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Adopt sending from the system; keep BDOI's file naming (C12, C23).</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Adopt sending from the system; keep BDOI's file naming (C12, C23).</t>
+          <t>Evidence of transmission.</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>Evidence of transmission.</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>PRD-019</t>
         </is>
@@ -2575,30 +2459,25 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Key-in of insurer terms with history; Marketing review of client-specific terms.</t>
+          <t>PRD-019: Programme negotiations are recorded in the system with each insurer's position per round.</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>PRD-019: Programme negotiations are recorded in the system with each insurer's position per round.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Adopt.</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Adopt.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>PRD-019</t>
         </is>
@@ -2627,30 +2506,25 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Comparative Table compiled from the responses, one master per request.</t>
+          <t>PRD-020: Comparisons are produced from captured terms, not re-keyed into spreadsheets.</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>PRD-020: Comparisons are produced from captured terms, not re-keyed into spreadsheets.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Adopt; QS value column (BDOI) as a platform change.</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Adopt; QS value column (BDOI) as a platform change.</t>
+          <t>No manual spreadsheets.</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>No manual spreadsheets.</t>
-        </is>
-      </c>
-      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>PRD-020</t>
         </is>
@@ -2681,32 +2555,27 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Requirements with signed package slip; ManCom approval in the system; forwarded to MBS; set-up and validation.</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
           <t>PRD-005: Rates are held in a rating engine, never keyed freely, and every quotation is re-priced on the server.
 PRD-017: Packaged programmes are quoted on the spot from maintained rates.
 PRD-021: Product approval by a management committee is evidenced before set-up.</t>
         </is>
       </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Extend</t>
+          <t>Adopt BDOI's parallel approvers then President routing (platform change).</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Adopt BDOI's parallel approvers then President routing (platform change).</t>
+          <t>ManCom evidence in the system.</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>ManCom evidence in the system.</t>
-        </is>
-      </c>
-      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>PRD-005, PRD-017, PRD-021</t>
         </is>
@@ -2735,30 +2604,25 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Advisories drafted on release with the supporting documents; sent to groups and by protected e-mail.</t>
+          <t>PRD-022: Sales and operations are told formally when a product goes live or changes.</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>PRD-022: Sales and operations are told formally when a product goes live or changes.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Name the recipient units.</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Name the recipient units.</t>
+          <t>Units informed formally.</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>Units informed formally.</t>
-        </is>
-      </c>
-      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>PRD-022</t>
         </is>
@@ -2787,30 +2651,25 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Daily expiry check with alerts; Package Expiry list; renewal requests generated from the version in force.</t>
+          <t>PRD-023: Programme renewals with insurers start well before expiry so terms are agreed in time.</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>PRD-023: Programme renewals with insurers start well before expiry so terms are agreed in time.</t>
+          <t>Extend</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Extend</t>
+          <t>Set 90 days; add the anniversary alert (platform change); decide automatic drafting.</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Set 90 days; add the anniversary alert (platform change); decide automatic drafting.</t>
+          <t>Renewals started in time.</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>Renewals started in time.</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>PRD-023</t>
         </is>
@@ -2839,30 +2698,25 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Package Status Update Report and Placement Update Report on request, PDF and Excel.</t>
+          <t>PRD-024: Management sees the product pipeline and expiring programmes at a glance.</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>PRD-024: Management sees the product pipeline and expiring programmes at a glance.</t>
+          <t>Extend</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Extend</t>
+          <t>Add the weekly Thursday 08:00 run with repository (platform change).</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Add the weekly Thursday 08:00 run with repository (platform change).</t>
+          <t>Weekly report without manual run.</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>Weekly report without manual run.</t>
-        </is>
-      </c>
-      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>PRD-024</t>
         </is>
@@ -2891,30 +2745,25 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Dashboard tiles by stage with overdue marking, expiring packages, validation queue.</t>
+          <t>PRD-024: Management sees the product pipeline and expiring programmes at a glance.</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>PRD-024: Management sees the product pipeline and expiring programmes at a glance.</t>
+          <t>Extend</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Extend</t>
+          <t>Add BDOI's KPIs, filters and PDF and CSV export (platform change).</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Add BDOI's KPIs, filters and PDF and CSV export (platform change).</t>
+          <t>Management visibility as BDOI specified.</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>Management visibility as BDOI specified.</t>
-        </is>
-      </c>
-      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>PRD-024</t>
         </is>
@@ -2944,31 +2793,26 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Every document e-mailed outside BDOI is password protected; password in a separate e-mail.</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
           <t>QPL-031: Personal data sent by e-mail is protected in line with the Data Privacy Act security measures.
 WFL-020: Protection of personal data in documents leaving the organisation (encryption or secure links).</t>
         </is>
       </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Recommend change</t>
+        </is>
+      </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Recommend change</t>
+          <t>Do not waive BRPM.020; give the password convention.</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Do not waive BRPM.020; give the password convention.</t>
+          <t>Data privacy of client and insurer documents.</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>Data privacy of client and insurer documents.</t>
-        </is>
-      </c>
-      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>QPL-031, WFL-020</t>
         </is>
@@ -2997,30 +2841,25 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Workflow enforcement; maker-checker; service levels with overdue alerts; reassignment.</t>
+          <t>PRD-018: New products follow a documented approval path before negotiation starts.</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>PRD-018: New products follow a documented approval path before negotiation starts.</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>Confirm the service levels.</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Confirm the service levels.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>PRD-018</t>
         </is>
@@ -3049,30 +2888,25 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Notifications at each step; product master changes recorded for other BDOI systems.</t>
+          <t>PRD-029: Product master data is shared by interface, not re-keyed.</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>PRD-029: Product master data is shared by interface, not re-keyed.</t>
+          <t>Extend</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Extend</t>
+          <t>Name the receiving systems, format and timing.</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Name the receiving systems, format and timing.</t>
+          <t>Data flow to BDOI systems.</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>Data flow to BDOI systems.</t>
-        </is>
-      </c>
-      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>PRD-029</t>
         </is>
@@ -3101,47 +2935,42 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Audit trail of every action that no user can change; per-record history; export.</t>
+          <t>Complete, unchangeable audit trail with old and new values, exportable for auditors.</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Complete, unchangeable audit trail with old and new values, exportable for auditors.</t>
+          <t>Extend</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Extend</t>
+          <t>Add old and new values of master changes and the export file name (platform change).</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Add old and new values of master changes and the export file name (platform change).</t>
+          <t>Complete audit for reviewers.</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Complete audit for reviewers.</t>
-        </is>
-      </c>
-      <c r="J35" s="12" t="inlineStr">
-        <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J35"/>
+  <autoFilter ref="A4:I35"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:J535">
+  <conditionalFormatting sqref="A5:I535">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G535" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fit" error="Choose a value from the list (Fit)." type="list">
+    <dataValidation sqref="F5:F535" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fit" error="Choose a value from the list (Fit)." type="list">
       <formula1>'Lists'!$A$2:$A$5</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_FitGap_BRD-03_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_FitGap_BRD-03_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +126,11 @@
       <color rgb="00004EA8"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -250,6 +255,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -944,7 +950,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1233,7 +1239,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1382,7 +1388,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2978,7 +2984,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3008,28 +3014,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Recommend change</t>
         </is>
@@ -3040,7 +3046,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8BRD vs OOTB vs Best Practice&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
